--- a/output/stock_quant_scores/ARM_info.xlsx
+++ b/output/stock_quant_scores/ARM_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG2"/>
+  <dimension ref="A1:FK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,235 +1006,255 @@
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>ipoExpectedDate</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1332,28 +1352,28 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>140.99</v>
+        <v>140.65</v>
       </c>
       <c r="V2" t="n">
-        <v>142.15</v>
+        <v>141</v>
       </c>
       <c r="W2" t="n">
-        <v>141.45</v>
+        <v>137.62</v>
       </c>
       <c r="X2" t="n">
-        <v>145.9953</v>
+        <v>141.0799</v>
       </c>
       <c r="Y2" t="n">
-        <v>140.99</v>
+        <v>140.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>142.15</v>
+        <v>141</v>
       </c>
       <c r="AA2" t="n">
-        <v>141.45</v>
+        <v>137.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>146</v>
+        <v>141.0799</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1362,40 +1382,40 @@
         <v>4.183</v>
       </c>
       <c r="AE2" t="n">
-        <v>220.10606</v>
+        <v>211.54544</v>
       </c>
       <c r="AF2" t="n">
-        <v>70.519424</v>
+        <v>67.776695</v>
       </c>
       <c r="AG2" t="n">
-        <v>3402320</v>
+        <v>3747484</v>
       </c>
       <c r="AH2" t="n">
-        <v>3402320</v>
+        <v>3747484</v>
       </c>
       <c r="AI2" t="n">
-        <v>4821242</v>
+        <v>4755495</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5912610</v>
+        <v>5058300</v>
       </c>
       <c r="AK2" t="n">
-        <v>5912610</v>
+        <v>5058300</v>
       </c>
       <c r="AL2" t="n">
-        <v>145.24</v>
+        <v>139.46</v>
       </c>
       <c r="AM2" t="n">
-        <v>146</v>
+        <v>139.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AP2" t="n">
-        <v>153879281664</v>
+        <v>147894435840</v>
       </c>
       <c r="AQ2" t="n">
         <v>80</v>
@@ -1410,13 +1430,13 @@
         <v>46.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>37.34028</v>
+        <v>35.887997</v>
       </c>
       <c r="AV2" t="n">
-        <v>145.354</v>
+        <v>144.6816</v>
       </c>
       <c r="AW2" t="n">
-        <v>136.36858</v>
+        <v>136.39073</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -1433,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>146798411776</v>
+        <v>145347575808</v>
       </c>
       <c r="BC2" t="n">
         <v>0.16961999</v>
@@ -1445,19 +1465,19 @@
         <v>1059263999</v>
       </c>
       <c r="BF2" t="n">
-        <v>15242896</v>
+        <v>15021853</v>
       </c>
       <c r="BG2" t="n">
-        <v>16241218</v>
+        <v>15409754</v>
       </c>
       <c r="BH2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.014400001</v>
+        <v>0.014199999</v>
       </c>
       <c r="BK2" t="n">
         <v>0.0015199999</v>
@@ -1466,19 +1486,19 @@
         <v>0.95734</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.1116</v>
+        <v>0.11</v>
       </c>
       <c r="BO2" t="n">
-        <v>1059263999</v>
+        <v>1086752898</v>
       </c>
       <c r="BP2" t="n">
         <v>6.617</v>
       </c>
       <c r="BQ2" t="n">
-        <v>21.954058</v>
+        <v>21.100195</v>
       </c>
       <c r="BR2" t="n">
         <v>1743379200</v>
@@ -1502,16 +1522,16 @@
         <v>2.06</v>
       </c>
       <c r="BY2" t="n">
-        <v>35.622</v>
+        <v>35.27</v>
       </c>
       <c r="BZ2" t="n">
-        <v>155.87</v>
+        <v>154.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.03715086</v>
+        <v>-0.023704648</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -1519,7 +1539,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>145.27</v>
+        <v>139.62</v>
       </c>
       <c r="CE2" t="n">
         <v>210</v>
@@ -1641,174 +1661,186 @@
       </c>
       <c r="DM2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Arm Holdings plc</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DN2" t="n">
-        <v>1758740002</v>
-      </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DQ2" t="n">
+        <v>1758931187</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1758916801</v>
+      </c>
+      <c r="DS2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>finmb_667281196</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="DS2" t="n">
+      <c r="DW2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="DU2" t="b">
+      <c r="DY2" t="b">
         <v>0</v>
       </c>
-      <c r="DV2" t="n">
-        <v>3.0356753</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>145.27</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
+      <c r="DZ2" t="n">
+        <v>-0.732313</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>139.62</v>
+      </c>
+      <c r="EB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1694698200000</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>139.62</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>137.62 - 141.0799</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>4755495</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>59.619995</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.7452499</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>80.0 - 182.88</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
+        <v>-43.26001</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.2365486</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-2.3704648</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1762372800</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1762372800</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>1762372800</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1753909200</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1753909200</v>
+      </c>
+      <c r="EV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EW2" t="n">
         <v>0.66</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EX2" t="n">
         <v>2.06</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EY2" t="n">
         <v>1.69014</v>
       </c>
-      <c r="EB2" t="n">
-        <v>85.95146</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.083999634</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.0005778969500000001</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>8.901427999999999</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.06527477499999999</v>
-      </c>
-      <c r="EG2" t="n">
+      <c r="EZ2" t="n">
+        <v>82.608536</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>-5.0615997</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>-0.034984406</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>3.2292633</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>0.02367656</v>
+      </c>
+      <c r="FE2" t="n">
         <v>15</v>
       </c>
-      <c r="EH2" t="n">
+      <c r="FF2" t="n">
         <v>0</v>
       </c>
-      <c r="EI2" t="inlineStr">
+      <c r="FG2" t="inlineStr">
         <is>
           <t>2023-09-14</t>
         </is>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="FH2" t="inlineStr">
         <is>
           <t>2.2 - Buy</t>
         </is>
       </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1694698200000</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>4.279999</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>141.45 - 146.0</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>4821242</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>65.270004</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>0.81587505</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>80.0 - 182.88</t>
-        </is>
-      </c>
-      <c r="EU2" t="n">
-        <v>-37.61</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>-0.20565398</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>-3.715086</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1762372800</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1762372800</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1762372800</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1753909200</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1753909200</v>
-      </c>
-      <c r="FC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FD2" t="inlineStr">
+      <c r="FI2" t="inlineStr">
         <is>
           <t>Arm Holdings plc</t>
         </is>
       </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>Arm Holdings plc</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
+      <c r="FJ2" t="inlineStr">
         <is>
           <t>Arm</t>
         </is>
       </c>
-      <c r="FG2" t="n">
-        <v>2.5525</v>
+      <c r="FK2" t="n">
+        <v>2.5277</v>
       </c>
     </row>
   </sheetData>
